--- a/Other/Timeline.xlsx
+++ b/Other/Timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremias/Desktop/UNIL/MASTER/PROJET_ISH/ijo-musi/Other/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53179465-351B-AF4E-8140-62563F40E6F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA3CF21-34EB-9F46-9B6D-1BB2526FCFBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2280" yWindow="2680" windowWidth="26260" windowHeight="15320" xr2:uid="{252B9170-3E69-A547-B30A-652D99D1926D}"/>
   </bookViews>
@@ -36,20 +36,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Événement</t>
   </si>
   <si>
-    <t>Rendu d'un rapport sur les jeux d'acquisition linguistique</t>
-  </si>
-  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Changement de sujet</t>
-  </si>
-  <si>
     <t>Changement d'enseignant encadrant le projet</t>
   </si>
   <si>
@@ -65,10 +59,19 @@
     <t>Établissement de la problématique</t>
   </si>
   <si>
-    <t>Rendu du game design document</t>
-  </si>
-  <si>
     <t>Premières lectures sur la recherche-création</t>
+  </si>
+  <si>
+    <t>Rendu du rapport sur les jeux d'acquisition linguistique (Annexe 1)</t>
+  </si>
+  <si>
+    <t>Abandon de l'éthique philosophique au profit de l'acquisition linguistique</t>
+  </si>
+  <si>
+    <t>Début de Transpositions Ludiques</t>
+  </si>
+  <si>
+    <t>Rendu du Game Design Document</t>
   </si>
 </sst>
 </file>
@@ -116,10 +119,10 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -135,14 +138,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0777D2D9-3021-9A41-BC32-D6B80F3669DB}" name="Table1" displayName="Table1" ref="A1:B10" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:B10" xr:uid="{0777D2D9-3021-9A41-BC32-D6B80F3669DB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B10">
-    <sortCondition ref="B1:B10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0777D2D9-3021-9A41-BC32-D6B80F3669DB}" name="Table1" displayName="Table1" ref="A1:B11" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:B11" xr:uid="{0777D2D9-3021-9A41-BC32-D6B80F3669DB}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B11">
+    <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{B5EE4061-C5B9-9040-B945-8F39F3842E4A}" name="Événement"/>
-    <tableColumn id="2" xr3:uid="{BA0FB998-0488-2F42-83BB-797DD4F58A7C}" name="Date" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{BA0FB998-0488-2F42-83BB-797DD4F58A7C}" name="Date" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -445,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A9DF45-34C1-9641-AA51-4B5E0BFE802C}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="114.1640625" customWidth="1"/>
@@ -457,12 +460,12 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1">
         <v>44887</v>
@@ -470,7 +473,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1">
         <v>45189</v>
@@ -478,7 +481,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1">
         <v>45272</v>
@@ -486,42 +489,42 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>45541</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>45569</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1">
-        <v>45819</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1">
-        <v>45995</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B9" s="1">
-        <v>46135</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -529,7 +532,15 @@
         <v>6</v>
       </c>
       <c r="B10" s="1">
-        <v>45833</v>
+        <v>45995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46135</v>
       </c>
     </row>
   </sheetData>
